--- a/1_05_comparativa.xlsx
+++ b/1_05_comparativa.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{48377AFD-3081-4068-B403-0442C611BFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28694E14-7D62-4A27-A4B5-124AED6056C3}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{48377AFD-3081-4068-B403-0442C611BFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{015851D2-1BFB-43C0-BAD5-8BA85D972C9D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3465" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS" sheetId="1" r:id="rId1"/>
@@ -111,6 +111,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,13 +417,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -430,18 +434,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>19.7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -449,7 +453,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -457,13 +461,13 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
     </row>
   </sheetData>

--- a/1_05_comparativa.xlsx
+++ b/1_05_comparativa.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{48377AFD-3081-4068-B403-0442C611BFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{015851D2-1BFB-43C0-BAD5-8BA85D972C9D}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{48377AFD-3081-4068-B403-0442C611BFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{202E4D99-3BF7-47B0-BB57-16DB95586152}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7560" yWindow="2628" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS" sheetId="1" r:id="rId1"/>
@@ -111,10 +111,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,7 +435,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="C2">
         <v>19.7</v>

--- a/1_05_comparativa.xlsx
+++ b/1_05_comparativa.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{48377AFD-3081-4068-B403-0442C611BFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{202E4D99-3BF7-47B0-BB57-16DB95586152}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FE6A83-6217-4E0B-A355-537B8542C8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7560" yWindow="2628" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5352" yWindow="2808" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS" sheetId="1" r:id="rId1"/>
@@ -435,7 +435,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>18.5</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>19.7</v>

--- a/1_05_comparativa.xlsx
+++ b/1_05_comparativa.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FE6A83-6217-4E0B-A355-537B8542C8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C509DE1E-AF1D-4EA4-AA21-F1E7CC3D1586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5352" yWindow="2808" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -435,7 +435,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>19.7</v>

--- a/1_05_comparativa.xlsx
+++ b/1_05_comparativa.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C509DE1E-AF1D-4EA4-AA21-F1E7CC3D1586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F2FE75-BB7B-42AE-ACB5-1AE446627A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5352" yWindow="2808" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -435,7 +435,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>50</v>
+        <v>18.5</v>
       </c>
       <c r="C2">
         <v>19.7</v>
